--- a/template/igstrand_template_IgI.xlsx
+++ b/template/igstrand_template_IgI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nih-my.sharepoint.com/personal/khaniyau2_nih_gov/Documents/_Data/project_ig_survey/igstrand_tmalign/paper_2d_mapping/code/input/igstrand_template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wangjiy\Documents\webgl\2D-template\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="8_{5A07550F-58EC-5D43-B58F-F88F2DC4543E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0124CB6-C10B-E44F-B05C-D0A37FDD0221}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CA5EC2-56F0-4834-9DD5-AF5C87ACF383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2600" yWindow="1660" windowWidth="27640" windowHeight="16940" xr2:uid="{3390BF8A-7716-464D-8643-7E026AA65E7A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{3390BF8A-7716-464D-8643-7E026AA65E7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t>NUMBERING</t>
   </si>
   <si>
     <t>IgI</t>
-  </si>
-  <si>
-    <t>8-Strands</t>
   </si>
   <si>
     <t>SHEET A</t>
@@ -152,13 +149,7 @@
     <t>Nt</t>
   </si>
   <si>
-    <t>check  6555</t>
-  </si>
-  <si>
-    <t>I added line</t>
-  </si>
-  <si>
-    <t>I added</t>
+    <t>9-Strands</t>
   </si>
 </sst>
 </file>
@@ -803,10 +794,18 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -814,14 +813,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1156,16 +1147,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A67B180A-8213-3F4E-96AF-EF936E0E4693}">
-  <dimension ref="A1:AC329"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:U329"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="3" width="4.33203125" customWidth="1"/>
-    <col min="4" max="16" width="5.83203125" customWidth="1"/>
-    <col min="17" max="21" width="4.33203125" customWidth="1"/>
-    <col min="22" max="22" width="12.83203125" customWidth="1"/>
+    <col min="1" max="3" width="4.375" customWidth="1"/>
+    <col min="4" max="16" width="5.875" customWidth="1"/>
+    <col min="17" max="21" width="4.375" customWidth="1"/>
+    <col min="22" max="22" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="20">
+    <row r="1" spans="1:21" ht="20.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1185,16 +1176,16 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="P1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="3"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:21">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1217,13 +1208,13 @@
       <c r="T2" s="5"/>
       <c r="U2" s="6"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:21">
       <c r="A3" s="4"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="7"/>
       <c r="E3" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="9"/>
@@ -1233,7 +1224,7 @@
       <c r="K3" s="5"/>
       <c r="L3" s="10"/>
       <c r="M3" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N3" s="10"/>
       <c r="O3" s="10"/>
@@ -1244,37 +1235,37 @@
       <c r="T3" s="5"/>
       <c r="U3" s="6"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:21">
       <c r="A4" s="4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="G4" s="13" t="s">
         <v>7</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>8</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="N4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="O4" s="12" t="s">
         <v>11</v>
-      </c>
-      <c r="O4" s="12" t="s">
-        <v>12</v>
       </c>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
@@ -1283,39 +1274,39 @@
       <c r="T4" s="5"/>
       <c r="U4" s="6"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:21">
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>14</v>
-      </c>
       <c r="F5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>13</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>14</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="N5" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="O5" s="12" t="s">
         <v>13</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="O5" s="12" t="s">
-        <v>14</v>
       </c>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
@@ -1324,39 +1315,39 @@
       <c r="T5" s="5"/>
       <c r="U5" s="6"/>
     </row>
-    <row r="6" spans="1:25" ht="20">
+    <row r="6" spans="1:21" ht="20.25">
       <c r="A6" s="4"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="F6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="G6" s="20" t="s">
         <v>17</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>18</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="L6" s="21" t="s">
+      <c r="M6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="22" t="s">
+      <c r="N6" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="23" t="s">
+      <c r="O6" s="24" t="s">
         <v>22</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>23</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
@@ -1365,7 +1356,7 @@
       <c r="T6" s="5"/>
       <c r="U6" s="6"/>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:21">
       <c r="A7" s="4"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1406,7 +1397,7 @@
       <c r="T7" s="5"/>
       <c r="U7" s="6"/>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:21">
       <c r="A8" s="4"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1419,7 +1410,7 @@
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -1431,24 +1422,24 @@
       <c r="T8" s="5"/>
       <c r="U8" s="6"/>
     </row>
-    <row r="9" spans="1:25" ht="17" thickBot="1">
+    <row r="9" spans="1:21" ht="16.5" thickBot="1">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="98" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="97"/>
+      <c r="D9" s="102" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="99"/>
       <c r="F9" s="5"/>
       <c r="G9" s="34"/>
       <c r="H9" s="34"/>
-      <c r="I9" s="99" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="100"/>
+      <c r="I9" s="103" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="104"/>
       <c r="K9" s="35"/>
       <c r="L9" s="36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M9" s="34"/>
       <c r="N9" s="34"/>
@@ -1460,7 +1451,7 @@
       <c r="T9" s="5"/>
       <c r="U9" s="6"/>
     </row>
-    <row r="10" spans="1:25" ht="18" thickTop="1" thickBot="1">
+    <row r="10" spans="1:21" ht="17.25" thickTop="1" thickBot="1">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1468,7 +1459,7 @@
       <c r="E10" s="5"/>
       <c r="F10" s="37"/>
       <c r="G10" s="43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H10" s="38">
         <v>6546</v>
@@ -1503,7 +1494,7 @@
       <c r="T10" s="5"/>
       <c r="U10" s="6"/>
     </row>
-    <row r="11" spans="1:25" ht="18" thickTop="1" thickBot="1">
+    <row r="11" spans="1:21" ht="17.25" thickTop="1" thickBot="1">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1512,10 +1503,10 @@
       <c r="F11" s="35"/>
       <c r="G11" s="35"/>
       <c r="H11" s="34"/>
-      <c r="I11" s="99" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="100"/>
+      <c r="I11" s="103" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="104"/>
       <c r="K11" s="35"/>
       <c r="L11" s="40"/>
       <c r="M11" s="34"/>
@@ -1528,7 +1519,7 @@
       <c r="T11" s="5"/>
       <c r="U11" s="6"/>
     </row>
-    <row r="12" spans="1:25" ht="21" thickTop="1" thickBot="1">
+    <row r="12" spans="1:21" ht="21" thickTop="1" thickBot="1">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1554,10 +1545,10 @@
         <v>8543</v>
       </c>
       <c r="M12" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="N12" s="84" t="s">
         <v>29</v>
-      </c>
-      <c r="N12" s="84" t="s">
-        <v>30</v>
       </c>
       <c r="O12" s="85"/>
       <c r="P12" s="37"/>
@@ -1566,11 +1557,8 @@
       <c r="S12" s="5"/>
       <c r="T12" s="5"/>
       <c r="U12" s="6"/>
-      <c r="Y12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="18" thickTop="1" thickBot="1">
+    </row>
+    <row r="13" spans="1:21" ht="17.25" thickTop="1" thickBot="1">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1584,7 +1572,7 @@
       <c r="G13" s="37"/>
       <c r="H13" s="34"/>
       <c r="I13" s="39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J13" s="38">
         <v>1853</v>
@@ -1597,7 +1585,7 @@
       </c>
       <c r="M13" s="37"/>
       <c r="N13" s="86" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O13" s="87"/>
       <c r="P13" s="37"/>
@@ -1607,7 +1595,7 @@
       <c r="T13" s="5"/>
       <c r="U13" s="6"/>
     </row>
-    <row r="14" spans="1:25" ht="17" thickTop="1">
+    <row r="14" spans="1:21" ht="16.5" thickTop="1">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -1628,10 +1616,10 @@
       </c>
       <c r="M14" s="37"/>
       <c r="N14" s="43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O14" s="41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P14" s="37"/>
       <c r="Q14" s="5"/>
@@ -1640,7 +1628,7 @@
       <c r="T14" s="5"/>
       <c r="U14" s="6"/>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:21">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1669,7 +1657,7 @@
       <c r="T15" s="5"/>
       <c r="U15" s="6"/>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:21">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1708,7 +1696,7 @@
       <c r="T16" s="5"/>
       <c r="U16" s="6"/>
     </row>
-    <row r="17" spans="1:29">
+    <row r="17" spans="1:21">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1747,7 +1735,7 @@
       <c r="T17" s="5"/>
       <c r="U17" s="6"/>
     </row>
-    <row r="18" spans="1:29" ht="17" thickBot="1">
+    <row r="18" spans="1:21" ht="16.5" thickBot="1">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1786,18 +1774,18 @@
       <c r="T18" s="5"/>
       <c r="U18" s="6"/>
     </row>
-    <row r="19" spans="1:29" ht="18" thickTop="1" thickBot="1">
+    <row r="19" spans="1:21" ht="17.25" thickTop="1" thickBot="1">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="37"/>
       <c r="D19" s="41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" s="59"/>
       <c r="F19" s="60"/>
       <c r="G19" s="61"/>
       <c r="H19" s="39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I19" s="39">
         <v>1552</v>
@@ -1827,7 +1815,7 @@
       <c r="T19" s="5"/>
       <c r="U19" s="6"/>
     </row>
-    <row r="20" spans="1:29" ht="17" thickTop="1">
+    <row r="20" spans="1:21" ht="16.5" thickTop="1">
       <c r="A20" s="4"/>
       <c r="B20" s="5"/>
       <c r="C20" s="37"/>
@@ -1858,7 +1846,7 @@
         <v>4549</v>
       </c>
       <c r="P20" s="41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
@@ -1866,7 +1854,7 @@
       <c r="T20" s="5"/>
       <c r="U20" s="6"/>
     </row>
-    <row r="21" spans="1:29">
+    <row r="21" spans="1:21">
       <c r="A21" s="4"/>
       <c r="B21" s="5"/>
       <c r="C21" s="37"/>
@@ -1899,7 +1887,7 @@
       <c r="T21" s="5"/>
       <c r="U21" s="6"/>
     </row>
-    <row r="22" spans="1:29">
+    <row r="22" spans="1:21">
       <c r="A22" s="4"/>
       <c r="B22" s="5"/>
       <c r="C22" s="37"/>
@@ -1916,12 +1904,12 @@
         <v>6552</v>
       </c>
       <c r="H22" s="68" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I22" s="69"/>
       <c r="J22" s="69"/>
       <c r="K22" s="70" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L22" s="44">
         <v>9550</v>
@@ -1942,7 +1930,7 @@
       <c r="T22" s="5"/>
       <c r="U22" s="6"/>
     </row>
-    <row r="23" spans="1:29">
+    <row r="23" spans="1:21">
       <c r="A23" s="4"/>
       <c r="B23" s="5"/>
       <c r="C23" s="37"/>
@@ -1973,7 +1961,7 @@
       <c r="T23" s="5"/>
       <c r="U23" s="6"/>
     </row>
-    <row r="24" spans="1:29">
+    <row r="24" spans="1:21">
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
       <c r="C24" s="37"/>
@@ -2011,20 +1999,8 @@
       <c r="S24" s="5"/>
       <c r="T24" s="5"/>
       <c r="U24" s="6"/>
-      <c r="Z24" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB24">
-        <v>6556</v>
-      </c>
-      <c r="AC24">
-        <v>7544</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29">
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
       <c r="C25" s="37"/>
@@ -2063,7 +2039,7 @@
       <c r="T25" s="5"/>
       <c r="U25" s="6"/>
     </row>
-    <row r="26" spans="1:29" ht="17" thickBot="1">
+    <row r="26" spans="1:21" ht="16.5" thickBot="1">
       <c r="A26" s="4"/>
       <c r="B26" s="5"/>
       <c r="C26" s="37"/>
@@ -2099,17 +2075,8 @@
       <c r="S26" s="5"/>
       <c r="T26" s="5"/>
       <c r="U26" s="6"/>
-      <c r="AA26" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB26">
-        <v>4555</v>
-      </c>
-      <c r="AC26">
-        <v>4556</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" ht="18" thickTop="1" thickBot="1">
+    </row>
+    <row r="27" spans="1:21" ht="17.25" thickTop="1" thickBot="1">
       <c r="A27" s="4"/>
       <c r="B27" s="5"/>
       <c r="C27" s="37"/>
@@ -2120,7 +2087,7 @@
         <v>2554</v>
       </c>
       <c r="F27" s="92" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" s="93">
         <v>6556</v>
@@ -2138,17 +2105,17 @@
       <c r="N27" s="72">
         <v>3546</v>
       </c>
-      <c r="O27" s="98" t="s">
-        <v>33</v>
-      </c>
-      <c r="P27" s="97"/>
+      <c r="O27" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="P27" s="99"/>
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5"/>
       <c r="U27" s="6"/>
     </row>
-    <row r="28" spans="1:29" ht="17" thickTop="1">
+    <row r="28" spans="1:21" ht="16.5" thickTop="1">
       <c r="A28" s="4"/>
       <c r="B28" s="5"/>
       <c r="C28" s="37"/>
@@ -2158,10 +2125,10 @@
       <c r="E28" s="72">
         <v>2555</v>
       </c>
-      <c r="F28" s="96" t="s">
-        <v>27</v>
-      </c>
-      <c r="G28" s="97"/>
+      <c r="F28" s="100" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="99"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
@@ -2183,7 +2150,7 @@
       <c r="T28" s="5"/>
       <c r="U28" s="6"/>
     </row>
-    <row r="29" spans="1:29" ht="20" thickBot="1">
+    <row r="29" spans="1:21" ht="20.25" thickBot="1">
       <c r="A29" s="4"/>
       <c r="B29" s="5"/>
       <c r="C29" s="37"/>
@@ -2191,16 +2158,16 @@
         <v>1543</v>
       </c>
       <c r="E29" s="76"/>
-      <c r="F29" s="101" t="s">
-        <v>34</v>
-      </c>
-      <c r="G29" s="102"/>
+      <c r="F29" s="96" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="97"/>
       <c r="H29" s="5"/>
       <c r="I29" s="34"/>
       <c r="J29" s="34"/>
       <c r="K29" s="37"/>
       <c r="L29" s="77" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M29" s="78">
         <v>8556</v>
@@ -2214,14 +2181,14 @@
       <c r="T29" s="5"/>
       <c r="U29" s="6"/>
     </row>
-    <row r="30" spans="1:29" ht="18" thickTop="1" thickBot="1">
+    <row r="30" spans="1:21" ht="17.25" thickTop="1" thickBot="1">
       <c r="A30" s="4"/>
       <c r="B30" s="5"/>
       <c r="C30" s="37"/>
       <c r="D30" s="76"/>
       <c r="E30" s="79"/>
       <c r="F30" s="73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G30" s="73">
         <v>2556</v>
@@ -2231,7 +2198,7 @@
       </c>
       <c r="I30" s="79"/>
       <c r="J30" s="73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K30" s="80">
         <v>3543</v>
@@ -2240,7 +2207,7 @@
         <v>3544</v>
       </c>
       <c r="M30" s="73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N30" s="40"/>
       <c r="O30" s="5"/>
@@ -2251,7 +2218,7 @@
       <c r="T30" s="5"/>
       <c r="U30" s="6"/>
     </row>
-    <row r="31" spans="1:29" ht="17" thickTop="1">
+    <row r="31" spans="1:21" ht="16.5" thickTop="1">
       <c r="A31" s="4"/>
       <c r="B31" s="5"/>
       <c r="C31" s="37"/>
@@ -2260,15 +2227,15 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
-      <c r="I31" s="103" t="s">
-        <v>35</v>
-      </c>
-      <c r="J31" s="97"/>
+      <c r="I31" s="98" t="s">
+        <v>34</v>
+      </c>
+      <c r="J31" s="99"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="96" t="s">
-        <v>27</v>
-      </c>
-      <c r="M31" s="97"/>
+      <c r="L31" s="100" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="99"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
@@ -2278,7 +2245,7 @@
       <c r="T31" s="5"/>
       <c r="U31" s="6"/>
     </row>
-    <row r="32" spans="1:29">
+    <row r="32" spans="1:21">
       <c r="A32" s="4"/>
       <c r="B32" s="5"/>
       <c r="C32" s="37"/>
@@ -2290,10 +2257,10 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
-      <c r="L32" s="103" t="s">
-        <v>36</v>
-      </c>
-      <c r="M32" s="97"/>
+      <c r="L32" s="98" t="s">
+        <v>35</v>
+      </c>
+      <c r="M32" s="99"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
@@ -2308,7 +2275,7 @@
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -2333,13 +2300,13 @@
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
       <c r="D34" s="33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
-      <c r="H34" s="104"/>
-      <c r="I34" s="97"/>
+      <c r="H34" s="101"/>
+      <c r="I34" s="99"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
@@ -2583,7 +2550,7 @@
       <c r="T44" s="5"/>
       <c r="U44" s="6"/>
     </row>
-    <row r="45" spans="1:21" ht="17" thickBot="1">
+    <row r="45" spans="1:21" ht="16.5" thickBot="1">
       <c r="A45" s="81"/>
       <c r="B45" s="81"/>
       <c r="C45" s="81"/>
@@ -9140,16 +9107,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="L31:M31"/>
     <mergeCell ref="L32:M32"/>
     <mergeCell ref="H34:I34"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I11:J11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
